--- a/E/RPROCL.xlsx
+++ b/E/RPROCL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
@@ -32,6 +32,24 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139397</t>
+  </si>
+  <si>
+    <t>AICE CRS BALL CNC 65</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>20142998</t>
+  </si>
+  <si>
+    <t>AICE CRS BALL MSCT65</t>
+  </si>
+  <si>
+    <t>261</t>
   </si>
 </sst>
 </file>
@@ -424,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -475,6 +493,46 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL.xlsx
+++ b/E/RPROCL.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135663</t>
-  </si>
-  <si>
-    <t>CMPN CNCRTO ICOWNC80</t>
+    <t>20140730</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO BROWNIE</t>
   </si>
   <si>
     <t>RPROCL</t>
@@ -28,7 +28,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>189</t>
+    <t>247</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -50,6 +50,24 @@
   </si>
   <si>
     <t>261</t>
+  </si>
+  <si>
+    <t>20141201</t>
+  </si>
+  <si>
+    <t>WALLS BALL GRAPE</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>20141200</t>
+  </si>
+  <si>
+    <t>WALLS BALL STRW GUAV</t>
+  </si>
+  <si>
+    <t>266</t>
   </si>
 </sst>
 </file>
@@ -442,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -533,6 +551,46 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL.xlsx
+++ b/E/RPROCL.xlsx
@@ -11,29 +11,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t/>
   </si>
   <si>
+    <t>20054385</t>
+  </si>
+  <si>
+    <t>WALLS NEO EXT.CRM350</t>
+  </si>
+  <si>
+    <t>RPROCL</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20115639</t>
+  </si>
+  <si>
+    <t>WALLS OREO VNL90</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>20140183</t>
+  </si>
+  <si>
+    <t>WALLS X PC PSL 90ML</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20140730</t>
   </si>
   <si>
     <t>CORNETTO CHO BROWNIE</t>
   </si>
   <si>
-    <t>RPROCL</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>247</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20139397</t>
   </si>
   <si>
@@ -43,6 +73,33 @@
     <t>248</t>
   </si>
   <si>
+    <t>20140731</t>
+  </si>
+  <si>
+    <t>WALLS AVOCDO BRW 350</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>20140732</t>
+  </si>
+  <si>
+    <t>WALLS MATCHA STW 350</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>20140087</t>
+  </si>
+  <si>
+    <t>WALLS FEAST MAX CHO</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
     <t>20142998</t>
   </si>
   <si>
@@ -68,6 +125,15 @@
   </si>
   <si>
     <t>266</t>
+  </si>
+  <si>
+    <t>20142871</t>
+  </si>
+  <si>
+    <t>WALL'S STRW CHS 350</t>
+  </si>
+  <si>
+    <t>267</t>
   </si>
 </sst>
 </file>
@@ -460,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -548,15 +614,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -565,18 +631,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -585,10 +651,150 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
